--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_183_R19.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_183_R19.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6425</v>
+        <v>9.478999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7495</v>
+        <v>7.5188</v>
       </c>
       <c r="F2" t="n">
-        <v>1.893</v>
+        <v>1.9602</v>
       </c>
       <c r="G2" t="n">
         <v>6.8017</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9067</v>
+        <v>0.9298</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5658</v>
+        <v>1.2035</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3409</v>
+        <v>-0.2737</v>
       </c>
       <c r="V2" t="n">
         <v>0.8197</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.468</v>
+        <v>5.2999</v>
       </c>
       <c r="E3" t="n">
         <v>4.2728</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1951</v>
+        <v>1.0271</v>
       </c>
       <c r="G3" t="n">
         <v>2.3405</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1971</v>
+        <v>1.0291</v>
       </c>
       <c r="T3" t="n">
         <v>1.2977</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1006</v>
+        <v>-0.2686</v>
       </c>
       <c r="V3" t="n">
         <v>1.4665</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8528</v>
+        <v>2.4381</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3431</v>
+        <v>0.1636</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5097</v>
+        <v>2.2745</v>
       </c>
       <c r="G4" t="n">
         <v>1.6023</v>
@@ -766,13 +766,13 @@
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4129</v>
+        <v>1.9982</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5074</v>
+        <v>2.3278</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0944</v>
+        <v>-0.3297</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9304</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>T. HEURTEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2495</v>
+        <v>0.9555</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2444</v>
+        <v>-1.0482</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.995</v>
+        <v>2.0037</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6519</v>
+        <v>-0.6635</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8726</v>
+        <v>-1.3628</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2207</v>
+        <v>0.6993</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3737</v>
+        <v>-0.4777</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1161</v>
+        <v>-1.4446</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2576</v>
+        <v>0.9669</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7219</v>
+        <v>-0.1858</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2435</v>
+        <v>0.0818</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4783</v>
+        <v>-0.2676</v>
       </c>
       <c r="P5" t="n">
+        <v>-0.4639</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-2.5515</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.0876</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.8689</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.214</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.214</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-1.3917</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.3917</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.7446</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.6567</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.08790000000000001</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-4.147</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.3943</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-3.7527</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1873</v>
+        <v>-0.0486</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2095</v>
+        <v>-0.4454</v>
       </c>
       <c r="F6" t="n">
         <v>0.3969</v>
@@ -922,10 +922,10 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>1.093</v>
+        <v>0.8571</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2151</v>
+        <v>0.9792</v>
       </c>
       <c r="U6" t="n">
         <v>-0.1221</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6495</v>
+        <v>-0.4136</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0912</v>
+        <v>-0.8552</v>
       </c>
       <c r="F7" t="n">
         <v>0.4416</v>
@@ -1000,10 +1000,10 @@
         <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4718</v>
+        <v>-0.2359</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2908</v>
+        <v>-0.0549</v>
       </c>
       <c r="U7" t="n">
         <v>-0.181</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. HEURTEL</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7288</v>
+        <v>-1.5706</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4636</v>
+        <v>1.3572</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7349</v>
+        <v>-2.9278</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6635</v>
+        <v>0.6519</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3628</v>
+        <v>0.8726</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6993</v>
+        <v>-0.2207</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4777</v>
+        <v>1.3737</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4446</v>
+        <v>1.1161</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9669</v>
+        <v>0.2576</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1858</v>
+        <v>-0.7219</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0818</v>
+        <v>-0.2435</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2676</v>
+        <v>-0.4783</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8153</v>
+        <v>1.9246</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6484</v>
+        <v>1.7695</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1669</v>
+        <v>0.1551</v>
       </c>
       <c r="V8" t="n">
-        <v>1.214</v>
+        <v>-4.147</v>
       </c>
       <c r="W8" t="n">
-        <v>1.214</v>
+        <v>-0.3943</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-3.7527</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1238</v>
+        <v>-1.5778</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7329</v>
+        <v>-0.8508</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3909</v>
+        <v>-0.727</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4275</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4481</v>
+        <v>-0.0059</v>
       </c>
       <c r="T9" t="n">
-        <v>0.13</v>
+        <v>0.0121</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3181</v>
+        <v>-0.018</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7135</v>
+        <v>-2.0509</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1247</v>
+        <v>-2.5965</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4112</v>
+        <v>0.5456</v>
       </c>
       <c r="G10" t="n">
         <v>0.0317</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1826</v>
+        <v>0.8452</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1993</v>
+        <v>0.7275</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0167</v>
+        <v>0.1177</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0114</v>
+        <v>-2.3652</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0292</v>
+        <v>-1.3831</v>
       </c>
       <c r="F11" t="n">
         <v>-0.9822</v>
@@ -1312,10 +1312,10 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3145</v>
+        <v>-0.6684</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4129</v>
+        <v>0.0591</v>
       </c>
       <c r="U11" t="n">
         <v>-0.7275</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7155</v>
+        <v>-3.1929</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6507</v>
+        <v>-1.061</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0647</v>
+        <v>-2.132</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4925</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2926</v>
+        <v>0.23</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0158</v>
+        <v>0.6056</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3084</v>
+        <v>-0.3756</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4665</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9908</v>
+        <v>-3.486</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8862</v>
+        <v>-3.6503</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1045</v>
+        <v>0.1643</v>
       </c>
       <c r="G13" t="n">
         <v>-3.9618</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4929</v>
+        <v>0.0119</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4323</v>
+        <v>-0.1964</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0606</v>
+        <v>0.2082</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.466800000000001</v>
+        <v>3.466899999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1.421800000000002</v>
+        <v>1.421899999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0451</v>
+        <v>2.0449</v>
       </c>
       <c r="G14" t="n">
-        <v>3.363</v>
+        <v>3.363000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0577</v>
+        <v>2.057700000000001</v>
       </c>
       <c r="I14" t="n">
         <v>1.305300000000001</v>
@@ -1525,7 +1525,7 @@
         <v>0.3995000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>4.516</v>
+        <v>4.515999999999998</v>
       </c>
       <c r="M14" t="n">
         <v>-1.5526</v>
@@ -1546,16 +1546,16 @@
         <v>16.237</v>
       </c>
       <c r="S14" t="n">
-        <v>7.7845</v>
+        <v>7.7846</v>
       </c>
       <c r="T14" t="n">
-        <v>9.497600000000002</v>
+        <v>9.4977</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.7131</v>
+        <v>-1.7133</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.3609</v>
+        <v>-5.360900000000001</v>
       </c>
       <c r="W14" t="n">
         <v>5.565</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2853</v>
+        <v>3.6391</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6315</v>
+        <v>2.5135</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6538</v>
+        <v>1.1256</v>
       </c>
       <c r="G15" t="n">
         <v>1.0843</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5465</v>
+        <v>-0.1926</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7512</v>
+        <v>0.6332</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2977</v>
+        <v>-0.8259</v>
       </c>
       <c r="V15" t="n">
         <v>1.3558</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0212</v>
+        <v>3.6211</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8214</v>
+        <v>2.6471</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1997</v>
+        <v>0.974</v>
       </c>
       <c r="G16" t="n">
         <v>1.1314</v>
@@ -1702,13 +1702,13 @@
         <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.4324</v>
+        <v>-0.8325</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7468</v>
+        <v>0.0788</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.6856</v>
+        <v>-0.9113</v>
       </c>
       <c r="V16" t="n">
         <v>1.4665</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8921</v>
+        <v>3.3451</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0957</v>
+        <v>4.2891</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2037</v>
+        <v>-0.944</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8467</v>
+        <v>1.5424</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2847</v>
+        <v>1.9674</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5620000000000001</v>
+        <v>-0.4251</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6329</v>
+        <v>2.6894</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0672</v>
+        <v>1.3213</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5657</v>
+        <v>1.3682</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7861</v>
+        <v>-1.1471</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2175</v>
+        <v>0.6462</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0037</v>
+        <v>-1.7933</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3917</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8676</v>
+        <v>-0.0532</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4629</v>
+        <v>0.7591</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5952</v>
+        <v>-0.8123</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.214</v>
+        <v>3.2476</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>4.3198</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8625</v>
+        <v>1.8151</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3455</v>
+        <v>0.4946</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.483</v>
+        <v>1.3205</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5424</v>
+        <v>-0.0866</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9674</v>
+        <v>0.0374</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4251</v>
+        <v>-0.124</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6894</v>
+        <v>0.2033</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3213</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3682</v>
+        <v>-0.4353</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1471</v>
+        <v>-0.2899</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6462</v>
+        <v>-0.6012</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7933</v>
+        <v>0.3113</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5358</v>
+        <v>-0.2761</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1845</v>
+        <v>0.2912</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3513</v>
+        <v>-0.5673</v>
       </c>
       <c r="V18" t="n">
-        <v>3.2476</v>
+        <v>-0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>4.3198</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.77</v>
+        <v>1.3537</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7305</v>
+        <v>2.388</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0395</v>
+        <v>-1.0343</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0866</v>
+        <v>0.8467</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0374</v>
+        <v>0.2847</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.124</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2033</v>
+        <v>1.6329</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.0672</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4353</v>
+        <v>1.5657</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2899</v>
+        <v>-0.7861</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6012</v>
+        <v>0.2175</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3113</v>
+        <v>-1.0037</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3211</v>
+        <v>0.3293</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5272</v>
+        <v>0.7551</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8483000000000001</v>
+        <v>-0.4259</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1418</v>
+        <v>-1.214</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1418</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6319</v>
+        <v>0.8577</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3946</v>
+        <v>-0.0772</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2373</v>
+        <v>0.9348</v>
       </c>
       <c r="G20" t="n">
         <v>1.1249</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1154</v>
+        <v>0.3411</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8259</v>
+        <v>0.3541</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2895</v>
+        <v>-0.013</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.521</v>
+        <v>-1.105</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0453</v>
+        <v>-1.8094</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5243</v>
+        <v>0.7044</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4983</v>
@@ -2092,13 +2092,13 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4892</v>
+        <v>-1.0732</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0455</v>
+        <v>-0.8096</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4437</v>
+        <v>-0.2636</v>
       </c>
       <c r="V21" t="n">
         <v>2.0026</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2331</v>
+        <v>-1.8177</v>
       </c>
       <c r="E22" t="n">
         <v>-2.4046</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1715</v>
+        <v>0.5869</v>
       </c>
       <c r="G22" t="n">
         <v>-3.0037</v>
@@ -2170,13 +2170,13 @@
         <v>2.3195</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4071</v>
+        <v>-0.9917</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3339</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0732</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5165</v>
+        <v>-2.0168</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6854</v>
+        <v>-2.5674</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1689</v>
+        <v>0.5506</v>
       </c>
       <c r="G23" t="n">
         <v>1.0753</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7361</v>
+        <v>-1.2364</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8962</v>
+        <v>-0.7782</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8399</v>
+        <v>-0.4582</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. STEVENS</t>
+          <t>A. M'BAYE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6699</v>
+        <v>-3.9678</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9364</v>
+        <v>-4.521</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7335</v>
+        <v>0.5531</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5439</v>
+        <v>-2.0354</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5736</v>
+        <v>0.7217</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9702</v>
+        <v>-2.7571</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.6292</v>
+        <v>-1.8389</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.2414</v>
+        <v>0.3361</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6122</v>
+        <v>-2.175</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9147</v>
+        <v>-0.1965</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.3856</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.5825</v>
+        <v>-0.5821</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0876</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q24" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>1.1756</v>
+        <v>-0.4531</v>
       </c>
       <c r="T24" t="n">
-        <v>2.0998</v>
+        <v>-0.275</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9243</v>
+        <v>-0.1781</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="W24" t="n">
         <v>1.0722</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. M'BAYE</t>
+          <t>L. STEVENS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.9894</v>
+        <v>-5.2596</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.9928</v>
+        <v>-2.9979</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0034</v>
+        <v>-2.2617</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.0354</v>
+        <v>-2.5439</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7217</v>
+        <v>-1.5736</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.7571</v>
+        <v>-0.9702</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.8389</v>
+        <v>-1.6292</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3361</v>
+        <v>-2.2414</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.175</v>
+        <v>0.6122</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1965</v>
+        <v>-0.9147</v>
       </c>
       <c r="N25" t="n">
-        <v>0.3856</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5821</v>
+        <v>-1.5825</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.5515</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q25" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4747</v>
+        <v>0.5858</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7468</v>
+        <v>1.0383</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7279</v>
+        <v>-0.4525</v>
       </c>
       <c r="V25" t="n">
-        <v>1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W25" t="n">
         <v>1.0722</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="26">
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.466900000000001</v>
+        <v>0.464900000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.045299999999999</v>
+        <v>-2.045199999999998</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.4218</v>
+        <v>2.5099</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.362899999999999</v>
+        <v>-3.3629</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.057799999999999</v>
+        <v>-2.0578</v>
       </c>
       <c r="I26" t="n">
         <v>-1.3051</v>
@@ -2467,7 +2467,7 @@
         <v>-4.9153</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.3994999999999999</v>
+        <v>-0.3995</v>
       </c>
       <c r="O26" t="n">
         <v>-4.516</v>
@@ -2482,16 +2482,16 @@
         <v>18.5562</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.7843</v>
+        <v>-3.8526</v>
       </c>
       <c r="T26" t="n">
-        <v>1.7133</v>
+        <v>1.7131</v>
       </c>
       <c r="U26" t="n">
-        <v>-9.4976</v>
+        <v>-5.565899999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>5.360900000000001</v>
+        <v>5.360899999999999</v>
       </c>
       <c r="W26" t="n">
         <v>10.9258</v>
